--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_01/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_01/design_variables_statistics.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,57 +429,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variável</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Desvio padrão</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>CV (%)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Mínimo</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1º quartil</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Mediana</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>3º quartil</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Máximo</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Amplitude</t>
         </is>
@@ -483,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>72.54000000000001</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>34.37</v>
+        <v>32.64</v>
       </c>
       <c r="E2" t="n">
-        <v>47.38</v>
+        <v>47.99</v>
       </c>
       <c r="F2" t="n">
-        <v>37.22</v>
+        <v>35.5</v>
       </c>
       <c r="G2" t="n">
-        <v>42.52</v>
+        <v>41.24</v>
       </c>
       <c r="H2" t="n">
-        <v>60.28</v>
+        <v>56.01</v>
       </c>
       <c r="I2" t="n">
-        <v>97.25</v>
+        <v>84.5</v>
       </c>
       <c r="J2" t="n">
-        <v>150</v>
+        <v>149.97</v>
       </c>
       <c r="K2" t="n">
-        <v>112.78</v>
+        <v>114.48</v>
       </c>
     </row>
     <row r="3">
@@ -520,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>19.43</v>
+        <v>16.68</v>
       </c>
       <c r="D3" t="n">
-        <v>15.16</v>
+        <v>14.5</v>
       </c>
       <c r="E3" t="n">
-        <v>78.02</v>
+        <v>86.94</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.05</v>
+        <v>5.01</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>5.08</v>
       </c>
       <c r="I3" t="n">
-        <v>33.68</v>
+        <v>33.44</v>
       </c>
       <c r="J3" t="n">
-        <v>40.69</v>
+        <v>40.43</v>
       </c>
       <c r="K3" t="n">
-        <v>35.69</v>
+        <v>35.43</v>
       </c>
     </row>
     <row r="4">
@@ -557,13 +569,13 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>7.2</v>
+        <v>7.84</v>
       </c>
       <c r="D4" t="n">
-        <v>3.81</v>
+        <v>4.38</v>
       </c>
       <c r="E4" t="n">
-        <v>52.87</v>
+        <v>55.87</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -572,16 +584,16 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>5.08</v>
+        <v>5.01</v>
       </c>
       <c r="I4" t="n">
-        <v>8.380000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="J4" t="n">
-        <v>18.89</v>
+        <v>17.69</v>
       </c>
       <c r="K4" t="n">
-        <v>13.89</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="5">
@@ -594,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>46.45</v>
+        <v>62.9</v>
       </c>
       <c r="D5" t="n">
-        <v>11.43</v>
+        <v>42.5</v>
       </c>
       <c r="E5" t="n">
-        <v>24.61</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>30.22</v>
+        <v>33.59</v>
       </c>
       <c r="G5" t="n">
-        <v>37.37</v>
+        <v>42.24</v>
       </c>
       <c r="H5" t="n">
-        <v>47.26</v>
+        <v>47.14</v>
       </c>
       <c r="I5" t="n">
-        <v>49.8</v>
+        <v>49.73</v>
       </c>
       <c r="J5" t="n">
-        <v>84.43000000000001</v>
+        <v>197.96</v>
       </c>
       <c r="K5" t="n">
-        <v>54.21</v>
+        <v>164.37</v>
       </c>
     </row>
     <row r="6">
@@ -631,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="D6" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>14.17</v>
+        <v>8.52</v>
       </c>
       <c r="F6" t="n">
-        <v>2.49</v>
+        <v>3.52</v>
       </c>
       <c r="G6" t="n">
-        <v>4.66</v>
+        <v>4.42</v>
       </c>
       <c r="H6" t="n">
-        <v>4.83</v>
+        <v>4.94</v>
       </c>
       <c r="I6" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="J6" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5</v>
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_01/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_01/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>61.37</v>
+        <v>62.29</v>
       </c>
       <c r="D2" t="n">
-        <v>17.56</v>
+        <v>16.3</v>
       </c>
       <c r="E2" t="n">
-        <v>28.6</v>
+        <v>26.16</v>
       </c>
       <c r="F2" t="n">
-        <v>41.59</v>
+        <v>43.3</v>
       </c>
       <c r="G2" t="n">
-        <v>46.66</v>
+        <v>49</v>
       </c>
       <c r="H2" t="n">
-        <v>55.07</v>
+        <v>57.93</v>
       </c>
       <c r="I2" t="n">
-        <v>73.17</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>58.41</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>37.78</v>
+        <v>37.63</v>
       </c>
       <c r="D3" t="n">
-        <v>2.24</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>5.92</v>
+        <v>10.62</v>
       </c>
       <c r="F3" t="n">
-        <v>33.44</v>
+        <v>21.37</v>
       </c>
       <c r="G3" t="n">
-        <v>38.78</v>
+        <v>38.58</v>
       </c>
       <c r="H3" t="n">
-        <v>38.78</v>
+        <v>38.59</v>
       </c>
       <c r="I3" t="n">
-        <v>38.79</v>
+        <v>38.61</v>
       </c>
       <c r="J3" t="n">
-        <v>40.59</v>
+        <v>39.1</v>
       </c>
       <c r="K3" t="n">
-        <v>7.15</v>
+        <v>17.73</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>6.47</v>
+        <v>7.41</v>
       </c>
       <c r="D4" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="E4" t="n">
-        <v>39.39</v>
+        <v>35.13</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>5.27</v>
       </c>
       <c r="H4" t="n">
-        <v>5.15</v>
+        <v>6.41</v>
       </c>
       <c r="I4" t="n">
-        <v>6.68</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>12.65</v>
+        <v>13.37</v>
       </c>
       <c r="K4" t="n">
-        <v>7.65</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>53.77</v>
+        <v>54.54</v>
       </c>
       <c r="D5" t="n">
-        <v>8.98</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>16.71</v>
+        <v>17.62</v>
       </c>
       <c r="F5" t="n">
-        <v>34.19</v>
+        <v>41.53</v>
       </c>
       <c r="G5" t="n">
-        <v>48.62</v>
+        <v>48.81</v>
       </c>
       <c r="H5" t="n">
-        <v>49.77</v>
+        <v>49.41</v>
       </c>
       <c r="I5" t="n">
-        <v>56.57</v>
+        <v>62.43</v>
       </c>
       <c r="J5" t="n">
-        <v>73.31</v>
+        <v>80.62</v>
       </c>
       <c r="K5" t="n">
-        <v>39.11</v>
+        <v>39.09</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>4.59</v>
+        <v>3.89</v>
       </c>
       <c r="D6" t="n">
-        <v>0.27</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>5.79</v>
+        <v>20.95</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9</v>
+        <v>2.01</v>
       </c>
       <c r="G6" t="n">
-        <v>4.43</v>
+        <v>3.92</v>
       </c>
       <c r="H6" t="n">
-        <v>4.57</v>
+        <v>4.17</v>
       </c>
       <c r="I6" t="n">
-        <v>4.83</v>
+        <v>4.39</v>
       </c>
       <c r="J6" t="n">
-        <v>4.99</v>
+        <v>4.77</v>
       </c>
       <c r="K6" t="n">
-        <v>1.09</v>
+        <v>2.76</v>
       </c>
     </row>
   </sheetData>
